--- a/models/sovereigns/Tajikistan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Tajikistan_Sovereign_Model.xlsx
@@ -671,16 +671,34 @@
           <t>cpi_latest_yoy_pct</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
+      <c r="B5" s="2" t="n">
+        <v>4.0609</v>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>IMF CPI database</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>IMF CPI database, all items, y/y % change, monthly (auto-filled; a run's sourced point replaces it unless older)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -949,7 +967,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>4.31</v>
+        <v>6.395</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -958,12 +976,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>World Bank WDI</t>
+          <t>IMF International Liquidity</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -973,7 +991,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+          <t>Gross official reserves incl. gold at national valuation, end-month (auto-filled; a run's sourced point replaces it unless older)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Tajikistan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Tajikistan_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 08-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/tajikistan.json</t>
+          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/tajikistan.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Tajikistan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Tajikistan_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 08-Oct-26</t>
+          <t>as of 09-Oct-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Tajikistan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Tajikistan_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/tajikistan.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/tajikistan.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Tajikistan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Tajikistan_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/tajikistan.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/tajikistan.json</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>19-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">

--- a/models/sovereigns/Tajikistan_Sovereign_Model.xlsx
+++ b/models/sovereigns/Tajikistan_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/tajikistan.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/tajikistan.json</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19-Oct-26</t>
+          <t>26-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
